--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
+        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410585&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410606&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור כהן - ארצנו הקטנטונת קאבר</v>
+        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קורין גמליאל - יהיה בסדר קאבר</v>
+        <v>אהרון כהן - תקופה חרא קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410581&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410605&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קורין גמליאל - יהיה בסדר קאבר</v>
+        <v>אהרון כהן - תקופה חרא קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
+        <v>אהרון כהן - לב לבן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410580&amp;sid=0a32e55cb67cd35689d741141f106de9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410604&amp;sid=b930a72629ecb842626bba50456fa521</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,12 +545,50 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עמנואל חסיד &amp; עדי חסיד - אצלנו בגן קאבר</v>
+        <v>אהרון כהן - לב לבן קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אהרון כהן - יפה בלבן קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410603&amp;sid=b930a72629ecb842626bba50456fa521</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אהרון כהן - יפה בלבן קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week04/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
+        <v>נועה שירי - לב שבור קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410606&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410638&amp;sid=a402efda2c448b65e7157027e659573c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר אלחייני - יש לי סיכוי קאבר</v>
+        <v>נועה שירי - לב שבור קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אהרון כהן - תקופה חרא קאבר</v>
+        <v>ליאור כהן - אהבתי הראשונה קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410605&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410637&amp;sid=a402efda2c448b65e7157027e659573c</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אהרון כהן - תקופה חרא קאבר</v>
+        <v>ליאור כהן - אהבתי הראשונה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אהרון כהן - לב לבן קאבר</v>
+        <v>דנה חן - אהובי קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410604&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410636&amp;sid=a402efda2c448b65e7157027e659573c</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אהרון כהן - לב לבן קאבר</v>
+        <v>דנה חן - אהובי קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אהרון כהן - יפה בלבן קאבר</v>
+        <v>גליה - יש לי חלום קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410603&amp;sid=b930a72629ecb842626bba50456fa521</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410635&amp;sid=a402efda2c448b65e7157027e659573c</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אהרון כהן - יפה בלבן קאבר</v>
+        <v>גליה - יש לי חלום קאבר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה שירי - לב שבור קאבר</v>
+        <v>שיר בלעיש - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410638&amp;sid=a402efda2c448b65e7157027e659573c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410639&amp;sid=8e6f38dfc3c99a038eabbdc986840695</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה שירי - לב שבור קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ליאור כהן - אהבתי הראשונה קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410637&amp;sid=a402efda2c448b65e7157027e659573c</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>ליאור כהן - אהבתי הראשונה קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>דנה חן - אהובי קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410636&amp;sid=a402efda2c448b65e7157027e659573c</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>דנה חן - אהובי קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>גליה - יש לי חלום קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410635&amp;sid=a402efda2c448b65e7157027e659573c</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>גליה - יש לי חלום קאבר</v>
+        <v>שיר בלעיש - לב לבן קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר בלעיש - לב לבן קאבר</v>
+        <v>רוני יחיא - שלווה בארמונותייך קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410639&amp;sid=8e6f38dfc3c99a038eabbdc986840695</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410644&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-28</v>
@@ -469,12 +469,126 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר בלעיש - לב לבן קאבר</v>
+        <v>רוני יחיא - שלווה בארמונותייך קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>עדן ששון - תמיד שמח קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410643&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>עדן ששון - תמיד שמח קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נויה לוי - אליס קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410642&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נויה לוי - אליס קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אפריים פייסחוב - אהבה אמיתית קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410641&amp;sid=c8639e896baa815c2db0ac77cccc86d0</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אפריים פייסחוב - אהבה אמיתית קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>